--- a/physics/first_term/labs/lab2/calc.xlsx
+++ b/physics/first_term/labs/lab2/calc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miwm64/itmo/practice/itmo_cse/physics/first_term/labs/lab2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75BF98B-DD78-FA42-ACCF-B4BDD1023459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C6CBE0-F5C4-5D47-8C2D-5BBD5F9070ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{A8378752-7FBB-B044-898E-5492180C3D03}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>x1</t>
   </si>
@@ -136,6 +136,42 @@
   </si>
   <si>
     <t>a_right</t>
+  </si>
+  <si>
+    <t>B=g</t>
+  </si>
+  <si>
+    <t>A=</t>
+  </si>
+  <si>
+    <t>ai*sinai</t>
+  </si>
+  <si>
+    <t>sina*sina</t>
+  </si>
+  <si>
+    <t>Sg=</t>
+  </si>
+  <si>
+    <t>di</t>
+  </si>
+  <si>
+    <t>D=</t>
+  </si>
+  <si>
+    <t>deltag=</t>
+  </si>
+  <si>
+    <t>di^2</t>
+  </si>
+  <si>
+    <t>St. Petersburg</t>
+  </si>
+  <si>
+    <t>δg=</t>
+  </si>
+  <si>
+    <t>Viktoria</t>
   </si>
 </sst>
 </file>
@@ -145,10 +181,17 @@
   <numFmts count="1">
     <numFmt numFmtId="167" formatCode="0.0000000000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -174,13 +217,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -518,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70844A8-4023-4B4B-8771-AF9A6E47F403}">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="10.83203125" style="1"/>
@@ -529,11 +573,12 @@
     <col min="15" max="15" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="10.83203125" style="1"/>
-    <col min="19" max="19" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="10.83203125" style="1"/>
+    <col min="19" max="19" width="17.5" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.33203125" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,7 +619,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0.15</v>
       </c>
@@ -631,8 +676,12 @@
         <f>SUM(N2:N6)/SUM(O2:O6)</f>
         <v>0.10783135505325717</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T2" s="1">
+        <f>S2*9</f>
+        <v>0.97048219547931447</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>0.15</v>
       </c>
@@ -690,7 +739,7 @@
         <v>3.9047566859377772E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>0.15</v>
       </c>
@@ -748,7 +797,7 @@
         <v>7.8095133718755544E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>0.15</v>
       </c>
@@ -806,7 +855,7 @@
         <v>7.2423400114173555</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>0.15</v>
       </c>
@@ -867,10 +916,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1244F8A3-8AD3-404D-948E-E16663B5E4A4}">
-  <dimension ref="A1:AF56"/>
+  <dimension ref="A1:AO56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="41" max="41" width="11.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>17</v>
       </c>
@@ -940,15 +992,27 @@
       <c r="AF1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
+      <c r="AH1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>0.191</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
         <v>0.183</v>
       </c>
       <c r="D2" s="1">
@@ -1038,11 +1102,34 @@
         <f>(POWER(U2*V2,2)+POWER(X2*Y2,2))/POWER(POWER(X2,2)-POWER(U2,2),2)</f>
         <v>7.962638566155366E-4</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
+      <c r="AH2">
+        <f>AA2*T2</f>
+        <v>1.4286788480336885E-3</v>
+      </c>
+      <c r="AI2">
+        <f>T2*T2</f>
+        <v>1.643655489809339E-4</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL2">
+        <f>(SUM(AH2:AH6)-1/5*SUM(AA2:AA6)*SUM(T2:T6))/(SUM(AI2:AI6)-1/5*POWER(SUM(T2:T6),2))</f>
+        <v>10.014690389949301</v>
+      </c>
+      <c r="AN2">
+        <f>AA2-($AL$3+$AL$2*T2)</f>
+        <v>-1.2172490019756593E-3</v>
+      </c>
+      <c r="AO2">
+        <f>POWER(AN2,2)</f>
+        <v>1.4816951328107387E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
       <c r="D3" s="1">
         <v>2</v>
       </c>
@@ -1130,11 +1217,34 @@
         <f t="shared" ref="AF3:AF6" si="4">(POWER(U3*V3,2)+POWER(X3*Y3,2))/POWER(POWER(X3,2)-POWER(U3,2),2)</f>
         <v>6.7456207810297133E-4</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="AH3">
+        <f t="shared" ref="AH3:AH6" si="5">AA3*T3</f>
+        <v>5.8735952833175115E-3</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" ref="AI3:AI6" si="6">T3*T3</f>
+        <v>6.5746219592373561E-4</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL3">
+        <f>1/5*(SUM(AA2:AA6)-AL2*SUM(T2:T6))</f>
+        <v>-1.5739267389208413E-2</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" ref="AN3:AN6" si="7">AA3-($AL$3+$AL$2*T3)</f>
+        <v>-1.1977449637032178E-2</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" ref="AO3:AO6" si="8">POWER(AN3,2)</f>
+        <v>1.4345929980764225E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="1">
         <v>3</v>
       </c>
@@ -1222,11 +1332,34 @@
         <f t="shared" si="4"/>
         <v>1.7720027989891949E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
+      <c r="AH4">
+        <f t="shared" si="5"/>
+        <v>1.2920574411822424E-2</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="6"/>
+        <v>1.2886259040105193E-3</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL4">
+        <f>SUM(AI2:AI6)-1/5*(POWER(SUM(T2:T6),2))</f>
+        <v>1.2754766600920437E-3</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="7"/>
+        <v>1.616784826981793E-2</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="8"/>
+        <v>2.6139931767585464E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
       <c r="D5" s="1">
         <v>4</v>
       </c>
@@ -1314,11 +1447,34 @@
         <f>(POWER(U5*V5,2)+POWER(X5*Y5,2))/POWER(POWER(X5,2)-POWER(U5,2),2)</f>
         <v>2.5276750004880923E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
+      <c r="AH5">
+        <f t="shared" si="5"/>
+        <v>2.0903010033444819E-2</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="6"/>
+        <v>2.1301775147928997E-3</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL5">
+        <f>SQRT(SUM(AO2:AO6)/(AL4*3))</f>
+        <v>0.37421117542442661</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="7"/>
+        <v>6.4213385777245335E-3</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="8"/>
+        <v>4.1233589129773336E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
       <c r="D6" s="1">
         <v>5</v>
       </c>
@@ -1406,15 +1562,38 @@
         <f t="shared" si="4"/>
         <v>1.5195893172083648E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
+      <c r="AH6">
+        <f t="shared" si="5"/>
+        <v>3.3348595848595862E-2</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="6"/>
+        <v>3.4779750164365564E-3</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL6">
+        <f>2*AL5</f>
+        <v>0.74842235084885322</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="7"/>
+        <v>-9.3944882085342796E-3</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="8"/>
+        <v>8.8256408700289611E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
         <v>2</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>0.20100000000000001</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>0.183</v>
       </c>
       <c r="D7" s="1">
@@ -1442,11 +1621,18 @@
         <f>SUM(X2:X6)/5</f>
         <v>2.7519999999999998</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
+      <c r="AK7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL7">
+        <f>AL6/AL2*100</f>
+        <v>7.4732450201352858</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
       <c r="D8" s="1">
         <v>2</v>
       </c>
@@ -1464,11 +1650,17 @@
         <f>POWER((F8-X$3), 2)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
+      <c r="AK8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
       <c r="D9" s="1">
         <v>3</v>
       </c>
@@ -1486,11 +1678,22 @@
         <f>POWER((F9-X$3), 2)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
+      <c r="AK9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL9">
+        <f>ABS(AL2-9.82)</f>
+        <v>0.19469038994930088</v>
+      </c>
+      <c r="AN9">
+        <f>0.06*AL2+AL3</f>
+        <v>0.58514215600774966</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
       <c r="D10" s="1">
         <v>4</v>
       </c>
@@ -1508,11 +1711,22 @@
         <f>POWER((F10-X$3), 2)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
+      <c r="AK10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL10">
+        <f>AL9/9.82*100</f>
+        <v>1.9825905290152837</v>
+      </c>
+      <c r="AN10">
+        <f>0.07*AL2+AL3</f>
+        <v>0.68528905990724276</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
       <c r="D11" s="1">
         <v>5</v>
       </c>
@@ -1531,14 +1745,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A12" s="6">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A12" s="7">
         <v>3</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>0.21</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>0.184</v>
       </c>
       <c r="D12" s="1">
@@ -1559,10 +1773,10 @@
         <v>4.0000000000000072E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
       <c r="D13" s="1">
         <v>2</v>
       </c>
@@ -1581,10 +1795,10 @@
         <v>4.0000000000000072E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
       <c r="D14" s="1">
         <v>3</v>
       </c>
@@ -1603,10 +1817,10 @@
         <v>4.0000000000000072E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
       <c r="D15" s="1">
         <v>4</v>
       </c>
@@ -1625,10 +1839,10 @@
         <v>6.4000000000000116E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
       <c r="D16" s="1">
         <v>5</v>
       </c>
@@ -1648,13 +1862,13 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="6">
+      <c r="A17" s="7">
         <v>4</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>0.219</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
         <v>0.185</v>
       </c>
       <c r="D17" s="1">
@@ -1676,9 +1890,9 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
       <c r="D18" s="1">
         <v>2</v>
       </c>
@@ -1698,9 +1912,9 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
       <c r="D19" s="1">
         <v>3</v>
       </c>
@@ -1720,9 +1934,9 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
       <c r="D20" s="1">
         <v>4</v>
       </c>
@@ -1742,9 +1956,9 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
       <c r="D21" s="1">
         <v>5</v>
       </c>
@@ -1764,13 +1978,13 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="6">
+      <c r="A22" s="7">
         <v>5</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="7">
         <v>0.23</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="7">
         <v>0.186</v>
       </c>
       <c r="D22" s="1">
@@ -1792,9 +2006,9 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
       <c r="D23" s="1">
         <v>2</v>
       </c>
@@ -1814,9 +2028,9 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
       <c r="D24" s="1">
         <v>3</v>
       </c>
@@ -1836,9 +2050,9 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
       <c r="D25" s="1">
         <v>4</v>
       </c>
@@ -1858,9 +2072,9 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
       <c r="D26" s="1">
         <v>5</v>
       </c>
